--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_19-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_19-10-2025.xlsx
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Error: Exceeded 30 redirects.</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Error: Exceeded 30 redirects.</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£31.40</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.building-supplies-online.co.uk/products/celotex-xr4000-insulation-pitched-roof-board-1200-x-2400mm?variant=55597620396416</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
